--- a/Testes/reescala/Teste populacao e gerações/Teste2/1_populacao_final.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste2/1_populacao_final.xlsx
@@ -3639,8 +3639,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -4674,8 +4674,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -10000,8 +10000,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -11035,8 +11035,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -14754,8 +14754,8 @@
       <c r="Q13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="4" t="n">
-        <v>1</v>
+      <c r="R13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>0</v>
@@ -15810,8 +15810,8 @@
       <c r="X22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" s="5" t="n">
-        <v>0</v>
+      <c r="Y22" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Z22" s="5" t="n">
         <v>0</v>
@@ -16361,8 +16361,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -17396,8 +17396,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -22722,8 +22722,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -23757,8 +23757,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -25147,7 +25147,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -29083,8 +29083,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -30118,8 +30118,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -35444,8 +35444,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -36479,8 +36479,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -37869,7 +37869,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -41805,8 +41805,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -42840,8 +42840,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -44230,7 +44230,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -48166,8 +48166,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -49201,8 +49201,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -50591,7 +50591,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" s="5" t="n">
         <v>0</v>
@@ -54527,8 +54527,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -55562,8 +55562,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -55834,8 +55834,8 @@
       <c r="AD38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE38" s="5" t="n">
-        <v>0</v>
+      <c r="AE38" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF38" s="5" t="n">
         <v>0</v>
@@ -60888,8 +60888,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -61923,8 +61923,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
